--- a/missacc_2027_growth_analysis/missacc_launch_plan_202608_202703.xlsx
+++ b/missacc_2027_growth_analysis/missacc_launch_plan_202608_202703.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="v50网格(产能200)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="v60网格(扩产能225)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="v60网格(2026-09修订)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="检查点与触发规则" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -70,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -85,6 +89,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -846,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -929,32 +934,34 @@
         <v>70</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>477</v>
+        <v>420</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>403(目标+55%)</t>
+        </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>【安全阀】80/月超历史峰值62：0-6月新款动销率&lt;50% 或单款收入连续两月恶化 → 回撤65-70/月，坑位还给BD</t>
+          <t>【已回撤】原80/月计划因9月稀释黄灯(≤6月新款单产$909→$990→$674月化)回撤至70/月;安全阀继续:动销率&lt;50%或单产同比连续两月恶化→再撤至60-65/月</t>
         </is>
       </c>
     </row>
@@ -988,12 +995,14 @@
       <c r="I3" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>1124</v>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>存量修复轨道已达标(见9月复盘)</t>
+        </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>同v50：钥匙是单款产出不是数量；9月产能未达225时第一个被砍</t>
+          <t>目标+86%(9月修订):增量主靠存量换图修复(已验证净增~$3,160/天)+单款产出阶梯;数量仍是上限不是任务</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1041,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>扩产能后管线从115恢复到180（与v50持平），2028管线不再被牺牲；8-10月主窗口120款</t>
+          <t>目标+43%(9月修订,同比+121%加速);8-10月主窗口40/月不变,窗口硬期限10月</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1080,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>【条件加码】10-11月检查：35-40/月节奏下动销率≥45%且单款≥$400 → 12-2月从Evening挪5-10坑位/月给BD；掉穿线维持220</t>
+          <t>目标+100%(9月修订)。【条件加码】10-11月检查达标→MOB回撤释放的10机动坑位/月归BD(12-2月);未达标→目标回落+95%,坑位转ED/Bride。注意:9月BD减速(同比+117%→+89%,客单价$109未向$90走),检查分量加重</t>
         </is>
       </c>
     </row>
@@ -1204,34 +1213,44 @@
         <v>210</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1350</v>
+        <v>1290</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>≤225/月</t>
+          <t>215固定+10机动/月</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09修订记录:MOB 80→70/月;10坑位/月转为机动配额(BD条件加码,未达标转ED/Bride);实际执行产能(7月衣服类300款/8月356款,按SPU前缀口径)远超规划200/225,差异待业务确认。依据:missacc_202609_checkpoint_review.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:K11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1242,7 +1261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1297,7 +1316,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>0-6月新款动销率&lt;50%，或单款收入低于去年同月且连续两月下滑 → MOB回撤至65-70/月，坑位还给BD；增长点数向Evening转移</t>
+          <t>0-6月新款动销率&lt;50%，或单款收入低于去年同月且连续两月下滑 → MOB回撤至65-70/月，坑位还给BD；增长点数向Evening转移。2026-09黄灯:≤6月单产$909(7月)→$990(8月)→$674(9月月化),网格已回撤70/月;10月全月数据复核</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1333,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>实际上新应达225款/月；未达标按 MOB &gt; Bride &gt; BM 优先级保配额，砍Evening</t>
+          <t>已复核:实际衣服类上新(SPU前缀口径)7月300/8月356款,远超规划225——产能口径与执行差异待业务确认;新款单产稀释与超量上新并存,先回撤MOB</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1367,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35-40款/月节奏下：0-6月新款动销率≥45% 且 单款产出≥$400 → 12-2月从Evening挪5-10坑位/月给BD；掉穿线维持220不加</t>
+          <t>35-40/月节奏下:0-6月新款动销率≥45%且单款产出≥$400→+100%目标维持且获MOB机动坑位10/月(12-2月);未达→回落+95%,坑位转ED/Bride。9月警示:同比+117%→+89%减速、客单价$109未降向$90、新款单产$220→$168→$103</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1418,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0-6月新款单SPU月收入应≥$400；未达则收紧选款门槛，空坑位按条件规则让给BD（宁缺毋滥，坑位使用率不考核）</t>
+          <t>双轨制:①新款轨:0-6月新款单SPU月收入≥$400(9月实测$170,受超量上新稀释);②存量轨:老款收入较8月基线+$560/天且换图批次回报不衰减(9月实测+$1,860/天,已达标)。存量轨已于9/15激活条件增量(ED目标+80→+86%)</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1435,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>应≥$450；未达则下调ED目标至+45%(v50)/+55%(v60)，缺口转MOB/BM超额空间，2-3月坑位减15-20/月转BD</t>
+          <t>新款轨应≥$450。双轨均未达→ED目标下调至+45%(v50)/+55%(v60);仅新款轨未达但存量轨保持→回撤条件增量至+80%,缺口转MOB/Bride</t>
         </is>
       </c>
     </row>
@@ -1434,6 +1453,23 @@
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>目标≥$500（参考自家3-6月队列已实测$523）；同步考核老款动销率18.9%→23-25%（每+1pp≈+$9.5K/月）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09(已完成)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9月中期复盘</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>结论:①ED双轨达标激活+86%/+98%(换图归因:430款,7月批次2.37x/8月批次1.78x vs 控制组0.98x,净增~$3,160/天,老款池覆盖率仅10%);②MOB稀释黄灯,回撤70/月,目标-5pp;③BD减速,+100%待10-11月检查护航;④Bride加速(同比+121%),+43%;⑤裙装整体9月同比+96%,动能未衰减。详见missacc_202609_checkpoint_review.md</t>
         </is>
       </c>
     </row>
